--- a/tools/importer/reports/import-category-landing.report.xlsx
+++ b/tools/importer/reports/import-category-landing.report.xlsx
@@ -40,7 +40,7 @@
     <t>sonpo/business.report.json</t>
   </si>
   <si>
-    <t>["hero-category","columns-product-nav","columns-showcase","cards-link-grid","columns-cta","columns-info-panel"]</t>
+    <t>["breadcrumb","hero-category","columns-product-nav","columns-showcase","cards-teaser","cards-teaser","cards-link-grid","columns-cta","columns-info-panel"]</t>
   </si>
   <si>
     <t>sonpo/business</t>
@@ -52,7 +52,7 @@
     <t>category-landing</t>
   </si>
   <si>
-    <t>2026-03-12T19:13:55.085Z</t>
+    <t>2026-03-13T14:07:58.379Z</t>
   </si>
   <si>
     <t>法人向け保険 | AIG損保</t>
@@ -64,13 +64,13 @@
     <t>sonpo/personal.report.json</t>
   </si>
   <si>
-    <t>["hero-category","columns-product-nav","columns-showcase","cards-link-grid","cards-link-grid","columns-cta","columns-info-panel"]</t>
+    <t>["breadcrumb","hero-category","columns-product-nav","columns-showcase","cards-teaser","cards-link-grid","cards-link-grid","columns-cta","columns-info-panel"]</t>
   </si>
   <si>
     <t>sonpo/personal</t>
   </si>
   <si>
-    <t>2026-03-09T12:50:45.889Z</t>
+    <t>2026-03-13T14:07:49.587Z</t>
   </si>
   <si>
     <t>個人向け保険 | AIG損保</t>
@@ -82,13 +82,13 @@
     <t>sonpo/business/hjk.report.json</t>
   </si>
   <si>
-    <t>["hero-category","cards-link-grid","columns-cta"]</t>
+    <t>["breadcrumb","hero-category","cards-link-grid","columns-cta"]</t>
   </si>
   <si>
     <t>sonpo/business/hjk</t>
   </si>
   <si>
-    <t>2026-03-12T19:14:57.101Z</t>
+    <t>2026-03-13T14:08:55.514Z</t>
   </si>
   <si>
     <t>法人会会員企業のための福利厚生制度 | 法人向け保険 | AIG損保</t>
@@ -103,7 +103,7 @@
     <t>sonpo/business/industry</t>
   </si>
   <si>
-    <t>2026-03-12T19:14:24.841Z</t>
+    <t>2026-03-13T14:08:28.757Z</t>
   </si>
   <si>
     <t>業種から探す | 法人向け保険 | AIG損保</t>
@@ -118,7 +118,7 @@
     <t>sonpo/business/nzk</t>
   </si>
   <si>
-    <t>2026-03-12T19:14:47.093Z</t>
+    <t>2026-03-13T14:08:47.757Z</t>
   </si>
   <si>
     <t>納税協会会員企業のための福祉制度 | 法人向け保険 | AIG損保</t>
@@ -130,13 +130,13 @@
     <t>sonpo/business/product.report.json</t>
   </si>
   <si>
-    <t>["hero-category","columns-product-nav","columns-product-nav","columns-product-nav","cards-link-grid","columns-cta"]</t>
+    <t>["breadcrumb","hero-category","columns-product-nav","columns-product-nav","columns-product-nav","cards-link-grid","columns-cta"]</t>
   </si>
   <si>
     <t>sonpo/business/product</t>
   </si>
   <si>
-    <t>2026-03-12T19:14:14.996Z</t>
+    <t>2026-03-13T14:08:16.982Z</t>
   </si>
   <si>
     <t>法人向け商品一覧 | 法人向け保険 | AIG損保</t>
@@ -151,7 +151,7 @@
     <t>sonpo/business/risk</t>
   </si>
   <si>
-    <t>2026-03-12T19:14:37.216Z</t>
+    <t>2026-03-13T14:08:38.429Z</t>
   </si>
   <si>
     <t>リスクから探す | 法人向け保険 | AIG損保</t>
@@ -163,13 +163,13 @@
     <t>sonpo/personal/product.report.json</t>
   </si>
   <si>
-    <t>["hero-category","columns-product-nav","columns-product-nav","cards-link-grid","cards-link-grid","columns-cta"]</t>
+    <t>["breadcrumb","hero-category","columns-product-nav","columns-product-nav","cards-link-grid","cards-link-grid","columns-cta"]</t>
   </si>
   <si>
     <t>sonpo/personal/product</t>
   </si>
   <si>
-    <t>2026-03-12T19:14:04.777Z</t>
+    <t>2026-03-13T14:08:07.661Z</t>
   </si>
   <si>
     <t>個人向け商品一覧 | 個人向け保険 | AIG損保</t>

--- a/tools/importer/reports/import-category-landing.report.xlsx
+++ b/tools/importer/reports/import-category-landing.report.xlsx
@@ -40,7 +40,7 @@
     <t>sonpo/business.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","hero-category","columns-product-nav","columns-showcase","cards-teaser","cards-teaser","cards-link-grid","columns-cta","columns-info-panel"]</t>
+    <t>["breadcrumb","hero-category","columns-product-nav","columns-showcase","cards-teaser","cards-teaser","cards-link-grid","cards-link-grid","cards-link-grid","columns-cta","columns-info-panel"]</t>
   </si>
   <si>
     <t>sonpo/business</t>
@@ -52,7 +52,7 @@
     <t>category-landing</t>
   </si>
   <si>
-    <t>2026-03-13T14:07:58.379Z</t>
+    <t>2026-03-17T10:39:44.950Z</t>
   </si>
   <si>
     <t>法人向け保険 | AIG損保</t>
@@ -70,7 +70,7 @@
     <t>sonpo/personal</t>
   </si>
   <si>
-    <t>2026-03-13T14:07:49.587Z</t>
+    <t>2026-03-17T10:39:32.247Z</t>
   </si>
   <si>
     <t>個人向け保険 | AIG損保</t>
@@ -88,7 +88,7 @@
     <t>sonpo/business/hjk</t>
   </si>
   <si>
-    <t>2026-03-13T14:08:55.514Z</t>
+    <t>2026-03-13T20:56:40.629Z</t>
   </si>
   <si>
     <t>法人会会員企業のための福利厚生制度 | 法人向け保険 | AIG損保</t>
@@ -103,7 +103,7 @@
     <t>sonpo/business/industry</t>
   </si>
   <si>
-    <t>2026-03-13T14:08:28.757Z</t>
+    <t>2026-03-17T10:40:07.132Z</t>
   </si>
   <si>
     <t>業種から探す | 法人向け保険 | AIG損保</t>
@@ -118,7 +118,7 @@
     <t>sonpo/business/nzk</t>
   </si>
   <si>
-    <t>2026-03-13T14:08:47.757Z</t>
+    <t>2026-03-13T20:56:33.275Z</t>
   </si>
   <si>
     <t>納税協会会員企業のための福祉制度 | 法人向け保険 | AIG損保</t>
@@ -130,13 +130,13 @@
     <t>sonpo/business/product.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","hero-category","columns-product-nav","columns-product-nav","columns-product-nav","cards-link-grid","columns-cta"]</t>
+    <t>["breadcrumb","hero-category","anchor-nav","columns-product-detail","columns-product-detail","columns-product-detail","columns-product-detail","columns-product-detail","columns-product-detail","columns-product-detail","cards-link-grid","columns-cta"]</t>
   </si>
   <si>
     <t>sonpo/business/product</t>
   </si>
   <si>
-    <t>2026-03-13T14:08:16.982Z</t>
+    <t>2026-03-17T10:03:06.638Z</t>
   </si>
   <si>
     <t>法人向け商品一覧 | 法人向け保険 | AIG損保</t>
@@ -151,7 +151,7 @@
     <t>sonpo/business/risk</t>
   </si>
   <si>
-    <t>2026-03-13T14:08:38.429Z</t>
+    <t>2026-03-17T10:39:56.275Z</t>
   </si>
   <si>
     <t>リスクから探す | 法人向け保険 | AIG損保</t>
@@ -163,13 +163,13 @@
     <t>sonpo/personal/product.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","hero-category","columns-product-nav","columns-product-nav","cards-link-grid","cards-link-grid","columns-cta"]</t>
+    <t>["breadcrumb","hero-category","anchor-nav","columns-product-detail","columns-product-detail","columns-product-detail","columns-product-detail","columns-product-detail","cards-link-grid","cards-link-grid","columns-cta"]</t>
   </si>
   <si>
     <t>sonpo/personal/product</t>
   </si>
   <si>
-    <t>2026-03-13T14:08:07.661Z</t>
+    <t>2026-03-17T10:02:51.270Z</t>
   </si>
   <si>
     <t>個人向け商品一覧 | 個人向け保険 | AIG損保</t>
